--- a/frontend/e2e/fixtures/ordine759.xlsx
+++ b/frontend/e2e/fixtures/ordine759.xlsx
@@ -422,7 +422,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ordine 759</t>
+          <t>ordine 907</t>
         </is>
       </c>
     </row>
